--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Cahangir\Desktop\test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CC7E05F-93A9-432E-A253-6A022D99A896}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0A74715-90CF-4A84-85FB-6D07724A4BCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -403,7 +403,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="1">
-        <v>1200</v>
+        <v>200</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Cahangir\Desktop\test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0A74715-90CF-4A84-85FB-6D07724A4BCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9F074E6-A527-464A-A8BD-6AA78E7B1DBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -403,7 +403,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="1">
-        <v>200</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
